--- a/output/leads_energy_storage_2026-07-31.xlsx
+++ b/output/leads_energy_storage_2026-07-31.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Energy Storage &amp; Bat" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Energy Storage &amp; Bat'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Energy Storage &amp; Bat'!$A$1:$I$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -520,30 +520,30 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sonnen GmbH</t>
+          <t>Tesla, Inc. (Energy Division)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Energy Retailer &amp; Aggregator</t>
+          <t>Energy storage manufacturer &amp; retailer</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (500-1000)</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -553,32 +553,32 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sonnen%20GmbH</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Tesla%2C%20Inc.%20%28Energy%20Division%29</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Pure-play residential storage brand, heavily reliant on cost-competitive Chinese cells and packs.</t>
+          <t>While they produce their own batteries, they may buy Chinese cells for non-core markets or to meet volume spikes, but competition limits reliance.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Sunrun Inc.</t>
+          <t>Centrica plc (British Gas)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Solar Installation Company</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>90</v>
+          <t>Energy retailer &amp; aggregator</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>65</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -598,32 +598,32 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sunrun%20Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Centrica%20plc%20%28British%20Gas%29</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Residential storage demand is price-sensitive, and Chinese batteries offer best cost per kWh.</t>
+          <t>UK home energy services and EV charging expansion could use Chinese batteries, but slower adoption due to regulatory and brand constraints.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RWE AG</t>
+          <t>CleanCo Queensland</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Renewable Energy Project Developer</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>90</v>
+          <t>Utility Company (Power Generation &amp; Distribution)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>65</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -643,37 +643,37 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=RWE%20AG</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=CleanCo%20Queensland</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Massive global renewables pipeline requires cost-effective utility-scale storage from China.</t>
+          <t>State-owned clean energy generator with growing storage needs, but procurement may favor local or allied partners.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Zenobe Energy</t>
+          <t>Zen Energy</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Microgrid Developer / Storage Asset Owner</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>90</v>
+          <t>Energy Retailer &amp; Aggregator</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mid-size (200-1000)</t>
+          <t>Medium (200-1000)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -688,32 +688,32 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Zenobe%20Energy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Zen%20Energy</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Zenobe specializes in battery storage and fleet electrification, and Chinese suppliers offer the cost and delivery speed they need for rapid deployment.</t>
+          <t>Focus on commercial and industrial storage solutions, but smaller scale may limit direct large-volume Chinese sourcing.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NextEra Energy, Inc.</t>
+          <t>JERA Co., Inc.</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Utility Company</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>85</v>
+          <t>Utility Company (Power Generation &amp; Distribution)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>55</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -733,42 +733,42 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NextEra%20Energy%2C%20Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=JERA%20Co.%2C%20Inc.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Aggressive renewable expansion and storage needs make Chinese BESS cost-competitive and scalable.</t>
+          <t>Large-scale energy trader and generator, but Japanese market dynamics favor domestic or Korean battery makers.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>E.ON SE</t>
+          <t>Nexus (Nexus Renewable Energy)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Energy Retailer &amp; Aggregator</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>85</v>
+          <t>Renewable Energy Project Developer</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
+          <t>Medium (200-1000)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -778,647 +778,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=E.ON%20SE</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Nexus%20%28Nexus%20Renewable%20Energy%29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Active in distributed energy and virtual power plants, seeking low-cost storage to scale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Octopus Energy Group</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Energy Retailer &amp; Aggregator</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Octopus%20Energy%20Group</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Octopus actively manages distributed storage and virtual power plants, and Chinese batteries provide the volume and price needed for their aggressive growth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>SolarEdge Technologies, Inc.</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Solar Installation Company</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=SolarEdge%20Technologies%2C%20Inc.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Needs competitive battery supply for integrated solar+storage offerings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>E.ON Energy Solutions (UK)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Energy Retailer &amp; Aggregator</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=E.ON%20Energy%20Solutions%20%28UK%29</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>UK market incentives for home storage drive demand for affordable Chinese batteries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Lightsource bp</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Renewable Energy Project Developer</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Lightsource%20bp</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>They pair solar with storage globally, and Chinese suppliers offer the scale and cost efficiency for their large project pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Duke Energy Corporation</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Utility Company</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Duke%20Energy%20Corporation</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Large grid modernization plans but may prefer domestic suppliers due to regulatory pressure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>EnBW Energie Baden-Württemberg AG</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Utility Company</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=EnBW%20Energie%20Baden-W%C3%BCrttemberg%20AG</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Expanding storage but may favor European suppliers for grid compliance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>SSE plc</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Utility (Power Generation &amp; Distribution)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=SSE%20plc</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>SSE is expanding renewable generation and grid-scale storage, and Chinese suppliers offer cost-competitive battery systems for their UK projects.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Southern Company</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Utility Company</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Southern%20Company</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Investing in storage but conservative procurement may limit Chinese sourcing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>AGL Energy Limited</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Utility (Power Generation &amp; Distribution)</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=AGL%20Energy%20Limited</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>AGL is retiring coal plants and needs grid-scale storage, but may prefer established Western brands for reliability, though Chinese pricing is attractive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SoftBank Energy (SB Energy)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Renewable Energy Project Developer</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=SoftBank%20Energy%20%28SB%20Energy%29</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>SB Energy develops large solar-plus-storage projects and is open to global suppliers, but may face political pressure to avoid Chinese tech.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Origin Energy Ltd</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Energy Retailer &amp; Aggregator</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Origin%20Energy%20Ltd</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Origin is investing in storage for retail and generation, but has conservative procurement and may favor proven non-Chinese suppliers initially.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Tokyo Electric Power Company (TEPCO)</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Utility (Power Generation &amp; Distribution)</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tokyo%20Electric%20Power%20Company%20%28TEPCO%29</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>TEPCO is investing in storage but has strong domestic supplier relationships and regulatory preferences, making Chinese imports less likely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Kansai Electric Power Co., Inc.</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Utility (Power Generation &amp; Distribution)</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kansai%20Electric%20Power%20Co.%2C%20Inc.</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Kansai Electric is cautious and tied to Japanese supply chains, so Chinese battery purchases would be limited to pilot projects.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Tesla Inc. (Australia operations)</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>EV Charging Network Operator / Storage Provider</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tesla%20Inc.%20%28Australia%20operations%29</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Tesla manufactures its own batteries and is a competitor, so they are unlikely to buy from Chinese exporters except for niche components.</t>
+          <t>Smaller Japanese developer with niche projects, unlikely to source directly from China due to local partnerships.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
+  <autoFilter ref="A1:I7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>